--- a/Configs/Datas/#ZZZ.HitEffect.xlsx
+++ b/Configs/Datas/#ZZZ.HitEffect.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9B84650-CBDC-4F5F-B7F0-88BED72A3297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D9282D6-D9A7-4C80-B3CD-49AE4D5A40E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="65">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -265,6 +265,22 @@
   </si>
   <si>
     <t>ModifyAttribute,Attacker,FirstHitOnly,Ellen_FlashFreeze,1,0,1,None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾莲_招架_轻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾莲_招架_重</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ModifyAttribute,Victim,FirstHitOnly,Daze,20,0,1,Parried</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ModifyAttribute,Victim,FirstHitOnly,Daze,40,0,1,Parried</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -659,7 +675,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="24.125" customWidth="1"/>
@@ -1230,6 +1246,34 @@
         <v>56</v>
       </c>
     </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B39" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39">
+        <v>1040016</v>
+      </c>
+      <c r="D39" t="s">
+        <v>61</v>
+      </c>
+      <c r="F39" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B40" t="s">
+        <v>52</v>
+      </c>
+      <c r="C40">
+        <v>1040017</v>
+      </c>
+      <c r="D40" t="s">
+        <v>62</v>
+      </c>
+      <c r="F40" t="s">
+        <v>64</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Configs/Datas/#ZZZ.HitEffect.xlsx
+++ b/Configs/Datas/#ZZZ.HitEffect.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D9282D6-D9A7-4C80-B3CD-49AE4D5A40E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A9F8B6B-B6C6-4E14-94CD-4692BDEA1DEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="80">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -281,6 +281,64 @@
   </si>
   <si>
     <t>ModifyAttribute,Victim,FirstHitOnly,Daze,40,0,1,Parried</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>青衣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,None,20,0,1,Shake|ModifyAttribute,Attacker,EveryHit,Energy,1,0,1,None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,None,20,0,1,Light|ModifyAttribute,Attacker,EveryHit,Energy,2,0,1,None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Attack_Nomal_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Attack_Nomal_02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Attack_Nomal_06</t>
+  </si>
+  <si>
+    <t>QingYi_Attack_Nomal_07</t>
+  </si>
+  <si>
+    <t>QingYi_Attack_Nomal_04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Attack_Nomal_05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Attack_Nomal_05_02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Attack_Branch_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Attack_Branch_02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Attack_Special</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Attack_ExSpecial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Attack_ExSpecial_02</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -675,7 +733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="24.125" customWidth="1"/>
@@ -1274,6 +1332,174 @@
         <v>64</v>
       </c>
     </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B41" t="s">
+        <v>65</v>
+      </c>
+      <c r="C41">
+        <v>1050000</v>
+      </c>
+      <c r="D41" t="s">
+        <v>68</v>
+      </c>
+      <c r="F41" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B42" t="s">
+        <v>65</v>
+      </c>
+      <c r="C42">
+        <v>1050010</v>
+      </c>
+      <c r="D42" t="s">
+        <v>69</v>
+      </c>
+      <c r="F42" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B43" t="s">
+        <v>65</v>
+      </c>
+      <c r="C43">
+        <v>1050020</v>
+      </c>
+      <c r="D43" t="s">
+        <v>72</v>
+      </c>
+      <c r="F43" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B44" t="s">
+        <v>65</v>
+      </c>
+      <c r="C44">
+        <v>1050030</v>
+      </c>
+      <c r="D44" t="s">
+        <v>73</v>
+      </c>
+      <c r="F44" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B45" t="s">
+        <v>65</v>
+      </c>
+      <c r="C45">
+        <v>1050040</v>
+      </c>
+      <c r="D45" t="s">
+        <v>74</v>
+      </c>
+      <c r="F45" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B46" t="s">
+        <v>65</v>
+      </c>
+      <c r="C46">
+        <v>1050050</v>
+      </c>
+      <c r="D46" t="s">
+        <v>70</v>
+      </c>
+      <c r="F46" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B47" t="s">
+        <v>65</v>
+      </c>
+      <c r="C47">
+        <v>1050060</v>
+      </c>
+      <c r="D47" t="s">
+        <v>71</v>
+      </c>
+      <c r="F47" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B48" t="s">
+        <v>65</v>
+      </c>
+      <c r="C48">
+        <v>1050070</v>
+      </c>
+      <c r="D48" t="s">
+        <v>75</v>
+      </c>
+      <c r="F48" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B49" t="s">
+        <v>65</v>
+      </c>
+      <c r="C49">
+        <v>1050080</v>
+      </c>
+      <c r="D49" t="s">
+        <v>76</v>
+      </c>
+      <c r="F49" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B50" t="s">
+        <v>65</v>
+      </c>
+      <c r="C50">
+        <v>1050090</v>
+      </c>
+      <c r="D50" t="s">
+        <v>77</v>
+      </c>
+      <c r="F50" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B51" t="s">
+        <v>65</v>
+      </c>
+      <c r="C51">
+        <v>1050100</v>
+      </c>
+      <c r="D51" t="s">
+        <v>78</v>
+      </c>
+      <c r="F51" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B52" t="s">
+        <v>65</v>
+      </c>
+      <c r="C52">
+        <v>1050110</v>
+      </c>
+      <c r="D52" t="s">
+        <v>79</v>
+      </c>
+      <c r="F52" t="s">
+        <v>59</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Configs/Datas/#ZZZ.HitEffect.xlsx
+++ b/Configs/Datas/#ZZZ.HitEffect.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A9F8B6B-B6C6-4E14-94CD-4692BDEA1DEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA2E8D7D-41C0-4955-86D1-3B204E95CA40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="91">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -245,25 +245,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Damage,Victim,EveryHit,None,20,0,1,Light|ModifyAttribute,Attacker,EveryHit,Energy,5,0,1,None</t>
-  </si>
-  <si>
-    <t>Damage,Victim,EveryHit,None,20,0,1,Light|ModifyAttribute,Attacker,EveryHit,Energy,5,0,1,None</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Damage,Victim,EveryHit,None,20,0,1,Light|ModifyAttribute,Attacker,FirstHitOnly,Ellen_FlashFreeze,3,0,1,None</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Damage,Victim,EveryHit,None,20,0,1,Light|ModifyAttribute,Attacker,FirstHitOnly,Ellen_FlashFreeze,1,0,1,None</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Damage,Victim,EveryHit,None,20,0,1,Light</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ModifyAttribute,Attacker,FirstHitOnly,Ellen_FlashFreeze,1,0,1,None</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -288,14 +269,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Damage,Victim,EveryHit,None,20,0,1,Shake|ModifyAttribute,Attacker,EveryHit,Energy,1,0,1,None</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Damage,Victim,EveryHit,None,20,0,1,Light|ModifyAttribute,Attacker,EveryHit,Energy,2,0,1,None</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>QingYi_Attack_Nomal_01</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -339,6 +312,71 @@
   </si>
   <si>
     <t>QingYi_Attack_ExSpecial_02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_ParryAid_H</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_ParryAid_L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_AssultAid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>侵蚀提尔锋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TyrflingInfected_Attack_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TyrflingInfected_Attack_02</t>
+  </si>
+  <si>
+    <t>TyrflingInfected_Attack_03</t>
+  </si>
+  <si>
+    <t>TyrflingInfected_Attack_04</t>
+  </si>
+  <si>
+    <t>TyrflingInfected_Attack_05</t>
+  </si>
+  <si>
+    <t>TyrflingInfected_Attack_06</t>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,None,1,0,1,Light|ModifyAttribute,Attacker,EveryHit,Energy,5,0,1,None</t>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,None,1,0,1,Light|ModifyAttribute,Attacker,EveryHit,Energy,5,0,1,None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,None,1,0,1,Shake|ModifyAttribute,Attacker,EveryHit,Energy,1,0,1,None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,None,1,0,1,Light|ModifyAttribute,Attacker,FirstHitOnly,Ellen_FlashFreeze,1,0,1,None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,None,1,0,1,Light|ModifyAttribute,Attacker,FirstHitOnly,Ellen_FlashFreeze,3,0,1,None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,None,1,0,1,Light</t>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,None,1,0,1,Light</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,None,1,0,1,Heavy</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -733,7 +771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="24.125" customWidth="1"/>
@@ -823,7 +861,7 @@
         <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="I5" s="1"/>
       <c r="K5" s="3"/>
@@ -839,7 +877,7 @@
         <v>20</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="I6" s="1"/>
       <c r="K6" s="2"/>
@@ -855,7 +893,7 @@
         <v>21</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="I7" s="1"/>
       <c r="K7" s="2"/>
@@ -871,7 +909,7 @@
         <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -885,7 +923,7 @@
         <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="G9" s="1"/>
       <c r="K9" s="2"/>
@@ -901,7 +939,7 @@
         <v>24</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="K10" s="2"/>
     </row>
@@ -916,7 +954,7 @@
         <v>25</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="K11" s="2"/>
     </row>
@@ -931,7 +969,7 @@
         <v>26</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="G12" s="1"/>
       <c r="K12" s="2"/>
@@ -947,7 +985,7 @@
         <v>27</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="K13" s="2"/>
     </row>
@@ -962,7 +1000,7 @@
         <v>29</v>
       </c>
       <c r="F14" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="G14" s="1"/>
       <c r="K14" s="2"/>
@@ -978,7 +1016,7 @@
         <v>30</v>
       </c>
       <c r="F15" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="K15" s="2"/>
     </row>
@@ -993,7 +1031,7 @@
         <v>31</v>
       </c>
       <c r="F16" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.2">
@@ -1007,7 +1045,7 @@
         <v>32</v>
       </c>
       <c r="F17" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.2">
@@ -1021,7 +1059,7 @@
         <v>33</v>
       </c>
       <c r="F18" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.2">
@@ -1035,7 +1073,7 @@
         <v>34</v>
       </c>
       <c r="F19" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.2">
@@ -1049,7 +1087,7 @@
         <v>35</v>
       </c>
       <c r="F20" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
@@ -1063,7 +1101,7 @@
         <v>36</v>
       </c>
       <c r="F21" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
@@ -1077,7 +1115,7 @@
         <v>37</v>
       </c>
       <c r="F22" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.2">
@@ -1091,7 +1129,7 @@
         <v>38</v>
       </c>
       <c r="F23" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.2">
@@ -1105,7 +1143,7 @@
         <v>39</v>
       </c>
       <c r="F24" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.2">
@@ -1119,7 +1157,7 @@
         <v>40</v>
       </c>
       <c r="F25" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.2">
@@ -1133,7 +1171,7 @@
         <v>43</v>
       </c>
       <c r="F26" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.2">
@@ -1147,7 +1185,7 @@
         <v>44</v>
       </c>
       <c r="F27" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.2">
@@ -1161,7 +1199,7 @@
         <v>45</v>
       </c>
       <c r="F28" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
@@ -1175,7 +1213,7 @@
         <v>41</v>
       </c>
       <c r="F29" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
@@ -1189,7 +1227,7 @@
         <v>48</v>
       </c>
       <c r="F30" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.2">
@@ -1203,7 +1241,7 @@
         <v>46</v>
       </c>
       <c r="F31" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.2">
@@ -1217,7 +1255,7 @@
         <v>47</v>
       </c>
       <c r="F32" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.2">
@@ -1231,7 +1269,7 @@
         <v>42</v>
       </c>
       <c r="F33" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.2">
@@ -1245,7 +1283,7 @@
         <v>49</v>
       </c>
       <c r="F34" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.2">
@@ -1259,7 +1297,7 @@
         <v>50</v>
       </c>
       <c r="F35" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.2">
@@ -1273,7 +1311,7 @@
         <v>51</v>
       </c>
       <c r="F36" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
@@ -1287,7 +1325,7 @@
         <v>53</v>
       </c>
       <c r="F37" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
@@ -1301,7 +1339,7 @@
         <v>54</v>
       </c>
       <c r="F38" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.2">
@@ -1312,10 +1350,10 @@
         <v>1040016</v>
       </c>
       <c r="D39" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F39" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.2">
@@ -1326,178 +1364,304 @@
         <v>1040017</v>
       </c>
       <c r="D40" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="F40" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B41" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C41">
         <v>1050000</v>
       </c>
       <c r="D41" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="F41" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B42" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C42">
         <v>1050010</v>
       </c>
       <c r="D42" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="F42" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B43" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C43">
         <v>1050020</v>
       </c>
       <c r="D43" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="F43" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C44">
         <v>1050030</v>
       </c>
       <c r="D44" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="F44" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B45" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C45">
         <v>1050040</v>
       </c>
       <c r="D45" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F45" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C46">
         <v>1050050</v>
       </c>
       <c r="D46" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="F46" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B47" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C47">
         <v>1050060</v>
       </c>
       <c r="D47" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="F47" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B48" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C48">
         <v>1050070</v>
       </c>
       <c r="D48" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="F48" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B49" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C49">
         <v>1050080</v>
       </c>
       <c r="D49" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="F49" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B50" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C50">
         <v>1050090</v>
       </c>
       <c r="D50" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="F50" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B51" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C51">
         <v>1050100</v>
       </c>
       <c r="D51" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="F51" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C52">
         <v>1050110</v>
       </c>
       <c r="D52" t="s">
+        <v>72</v>
+      </c>
+      <c r="F52" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B53" t="s">
+        <v>60</v>
+      </c>
+      <c r="C53">
+        <v>1050120</v>
+      </c>
+      <c r="D53" t="s">
+        <v>73</v>
+      </c>
+      <c r="F53" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B54" t="s">
+        <v>60</v>
+      </c>
+      <c r="C54">
+        <v>1050130</v>
+      </c>
+      <c r="D54" t="s">
+        <v>74</v>
+      </c>
+      <c r="F54" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B55" t="s">
+        <v>60</v>
+      </c>
+      <c r="C55">
+        <v>1050140</v>
+      </c>
+      <c r="D55" t="s">
+        <v>75</v>
+      </c>
+      <c r="F55" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B56" t="s">
+        <v>76</v>
+      </c>
+      <c r="C56">
+        <v>9000000</v>
+      </c>
+      <c r="D56" t="s">
+        <v>77</v>
+      </c>
+      <c r="F56" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B57" t="s">
+        <v>76</v>
+      </c>
+      <c r="C57">
+        <v>9000010</v>
+      </c>
+      <c r="D57" t="s">
+        <v>78</v>
+      </c>
+      <c r="F57" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B58" t="s">
+        <v>76</v>
+      </c>
+      <c r="C58">
+        <v>9000020</v>
+      </c>
+      <c r="D58" t="s">
         <v>79</v>
       </c>
-      <c r="F52" t="s">
-        <v>59</v>
+      <c r="F58" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B59" t="s">
+        <v>76</v>
+      </c>
+      <c r="C59">
+        <v>9000030</v>
+      </c>
+      <c r="D59" t="s">
+        <v>80</v>
+      </c>
+      <c r="F59" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B60" t="s">
+        <v>76</v>
+      </c>
+      <c r="C60">
+        <v>9000040</v>
+      </c>
+      <c r="D60" t="s">
+        <v>81</v>
+      </c>
+      <c r="F60" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B61" t="s">
+        <v>76</v>
+      </c>
+      <c r="C61">
+        <v>9000050</v>
+      </c>
+      <c r="D61" t="s">
+        <v>82</v>
+      </c>
+      <c r="F61" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/Datas/#ZZZ.HitEffect.xlsx
+++ b/Configs/Datas/#ZZZ.HitEffect.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA2E8D7D-41C0-4955-86D1-3B204E95CA40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5550C7A1-2DFC-45D7-A12F-B8F4440175DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="76">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -67,12 +67,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>安比</t>
-  </si>
-  <si>
-    <t>星见雅</t>
-  </si>
-  <si>
     <t>#Remark</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -97,86 +91,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>安比</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>安比_普通攻击1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>安比_普通攻击2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>安比_普通攻击3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>安比_普通攻击4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>安比_普通攻击4_落雷</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>安比_特殊技</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>安比_特殊技_快速</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>安比_强化特殊技</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>安比_强化特殊技_快速</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>星见雅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>星见雅_普通攻击_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>星见雅_普通攻击_2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>星见雅_普通攻击_3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>星见雅_普通攻击_4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>星见雅_普通攻击_5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>星见雅_特殊技_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>星见雅_特殊技_1_无前摇</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>星见雅_终极技</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>星见雅_冲刺攻击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>艾莲乔_普通攻击_1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -241,10 +155,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>艾莲_普通攻击_霜降</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ModifyAttribute,Attacker,FirstHitOnly,Ellen_FlashFreeze,1,0,1,None</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -350,25 +260,6 @@
     <t>TyrflingInfected_Attack_06</t>
   </si>
   <si>
-    <t>Damage,Victim,EveryHit,None,1,0,1,Light|ModifyAttribute,Attacker,EveryHit,Energy,5,0,1,None</t>
-  </si>
-  <si>
-    <t>Damage,Victim,EveryHit,None,1,0,1,Light|ModifyAttribute,Attacker,EveryHit,Energy,5,0,1,None</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Damage,Victim,EveryHit,None,1,0,1,Shake|ModifyAttribute,Attacker,EveryHit,Energy,1,0,1,None</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Damage,Victim,EveryHit,None,1,0,1,Light|ModifyAttribute,Attacker,FirstHitOnly,Ellen_FlashFreeze,1,0,1,None</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Damage,Victim,EveryHit,None,1,0,1,Light|ModifyAttribute,Attacker,FirstHitOnly,Ellen_FlashFreeze,3,0,1,None</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Damage,Victim,EveryHit,None,1,0,1,Light</t>
   </si>
   <si>
@@ -377,6 +268,53 @@
   </si>
   <si>
     <t>Damage,Victim,EveryHit,None,1,0,1,Heavy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,None,1,0,1,Light|ModifyAttribute,Attacker,EveryHit,Energy,5,0,1,None |ModifyAttribute,Victim,EveryHit,Daze,1,0,1,None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,None,1,0,1,Light|ModifyAttribute,Attacker,EveryHit,Energy,5,0,1,None |ModifyAttribute,Victim,EveryHit,Daze,1,0,2,None</t>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,None,1,0,1,Light|ModifyAttribute,Attacker,EveryHit,Energy,5,0,1,None |ModifyAttribute,Victim,EveryHit,Daze,1,0,3,None</t>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,None,1,0,1,Light|ModifyAttribute,Attacker,EveryHit,Energy,5,0,1,None |ModifyAttribute,Victim,EveryHit,Daze,1,0,4,None</t>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,None,1,0,1,Light|ModifyAttribute,Attacker,EveryHit,Energy,5,0,1,None |ModifyAttribute,Victim,EveryHit,Daze,1,0,5,None</t>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,None,1,0,1,Light|ModifyAttribute,Attacker,EveryHit,Energy,5,0,1,None |ModifyAttribute,Victim,EveryHit,Daze,1,0,6,None</t>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,None,1,0,1,Light|ModifyAttribute,Attacker,EveryHit,Energy,5,0,1,None |ModifyAttribute,Victim,EveryHit,Daze,1,0,7,None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,None,1,0,1,Light|ModifyAttribute,Attacker,FirstHitOnly,Ellen_FlashFreeze,1,0,1,None|ModifyAttribute,Victim,EveryHit,Daze,1,0,7,None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,None,1,0,1,Light|ModifyAttribute,Attacker,FirstHitOnly,Ellen_FlashFreeze,3,0,1,None|ModifyAttribute,Victim,EveryHit,Daze,1,0,7,None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,None,1,0,1,Light|ModifyAttribute,Attacker,EveryHit,Energy,5,0,1,None|ModifyAttribute,Victim,EveryHit,Daze,1,0,7,None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,None,1,0,1,Light|ModifyAttribute,Victim,EveryHit,Daze,1,0,7,None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾莲_普通攻击_霜锋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage,Victim,EveryHit,None,1,0,1,Shake|ModifyAttribute,Attacker,EveryHit,Energy,1,0,1,None|ModifyAttribute,Victim,EveryHit,Daze,1,0,7,None</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -472,6 +410,20 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{53897227-ADB8-4B53-B1A9-ECAA3D3F7188}" name="表1" displayName="表1" ref="B4:F43" totalsRowShown="0">
+  <autoFilter ref="B4:F43" xr:uid="{53897227-ADB8-4B53-B1A9-ECAA3D3F7188}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{EAEFFCDA-04E0-45E0-B42E-209F2CC7D392}" name="角色名称"/>
+    <tableColumn id="2" xr3:uid="{4E2C7744-FAF1-469D-B6B7-DF135D5C3320}" name="id"/>
+    <tableColumn id="3" xr3:uid="{AD83571F-A142-46FE-8758-C1F892958023}" name="名称"/>
+    <tableColumn id="4" xr3:uid="{38348834-D0DB-40A6-8614-37ABEE3E9A48}" name="描述"/>
+    <tableColumn id="5" xr3:uid="{0F0CD659-8EF4-43BE-AA5F-4885987B6CAD}" name="命中效果列表"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -771,9 +723,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="2" max="2" width="10.25" customWidth="1"/>
     <col min="4" max="4" width="24.125" customWidth="1"/>
     <col min="5" max="5" width="39.625" customWidth="1"/>
     <col min="6" max="6" width="91.125" customWidth="1"/>
@@ -787,7 +740,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -799,7 +752,7 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -816,7 +769,7 @@
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I2" s="1"/>
       <c r="K2" s="2"/>
@@ -839,833 +792,584 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I4" s="1"/>
       <c r="K4" s="2"/>
     </row>
     <row r="5" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C5">
-        <v>1010000</v>
+        <v>1040000</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="I5" s="1"/>
       <c r="K5" s="3"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C6">
-        <v>1010001</v>
+        <v>1040001</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="I6" s="1"/>
       <c r="K6" s="2"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C7">
-        <v>1010002</v>
+        <v>1040002</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F7" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="I7" s="1"/>
       <c r="K7" s="2"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C8">
-        <v>1010003</v>
+        <v>1040003</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F8" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C9">
-        <v>1010004</v>
+        <v>1040004</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="G9" s="1"/>
       <c r="K9" s="2"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C10">
-        <v>1010005</v>
+        <v>1040005</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="K10" s="2"/>
     </row>
     <row r="11" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C11">
-        <v>1010006</v>
+        <v>1040006</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="K11" s="2"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C12">
-        <v>1010007</v>
+        <v>1040007</v>
       </c>
       <c r="D12" t="s">
         <v>26</v>
       </c>
       <c r="F12" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G12" s="1"/>
       <c r="K12" s="2"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C13">
-        <v>1010008</v>
+        <v>1040008</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F13" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="K13" s="2"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C14">
-        <v>1020000</v>
+        <v>1040009</v>
       </c>
       <c r="D14" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F14" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="G14" s="1"/>
       <c r="K14" s="2"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C15">
-        <v>1020001</v>
+        <v>1040010</v>
       </c>
       <c r="D15" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F15" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="K15" s="2"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C16">
-        <v>1020002</v>
+        <v>1040011</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F16" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C17">
-        <v>1020003</v>
+        <v>1040012</v>
       </c>
       <c r="D17" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F17" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C18">
-        <v>1020004</v>
+        <v>1040013</v>
       </c>
       <c r="D18" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F18" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C19">
-        <v>1020005</v>
+        <v>1040014</v>
       </c>
       <c r="D19" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F19" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C20">
-        <v>1020006</v>
+        <v>1040015</v>
       </c>
       <c r="D20" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="F20" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C21">
-        <v>1020007</v>
+        <v>1040016</v>
       </c>
       <c r="D21" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F21" t="s">
-        <v>83</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C22">
-        <v>1020008</v>
+        <v>1040017</v>
       </c>
       <c r="D22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F22" t="s">
-        <v>83</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C23">
-        <v>1040000</v>
+        <v>1050000</v>
       </c>
       <c r="D23" t="s">
         <v>38</v>
       </c>
       <c r="F23" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C24">
-        <v>1040001</v>
+        <v>1050010</v>
       </c>
       <c r="D24" t="s">
         <v>39</v>
       </c>
       <c r="F24" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C25">
-        <v>1040002</v>
+        <v>1050020</v>
       </c>
       <c r="D25" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F25" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C26">
-        <v>1040003</v>
+        <v>1050030</v>
       </c>
       <c r="D26" t="s">
         <v>43</v>
       </c>
       <c r="F26" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C27">
-        <v>1040004</v>
+        <v>1050040</v>
       </c>
       <c r="D27" t="s">
         <v>44</v>
       </c>
       <c r="F27" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C28">
-        <v>1040005</v>
+        <v>1050050</v>
       </c>
       <c r="D28" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F28" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C29">
-        <v>1040006</v>
+        <v>1050060</v>
       </c>
       <c r="D29" t="s">
         <v>41</v>
       </c>
       <c r="F29" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C30">
-        <v>1040007</v>
+        <v>1050070</v>
       </c>
       <c r="D30" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F30" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C31">
-        <v>1040008</v>
+        <v>1050080</v>
       </c>
       <c r="D31" t="s">
         <v>46</v>
       </c>
       <c r="F31" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C32">
-        <v>1040009</v>
+        <v>1050090</v>
       </c>
       <c r="D32" t="s">
         <v>47</v>
       </c>
       <c r="F32" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C33">
-        <v>1040010</v>
+        <v>1050100</v>
       </c>
       <c r="D33" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F33" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C34">
-        <v>1040011</v>
+        <v>1050110</v>
       </c>
       <c r="D34" t="s">
         <v>49</v>
       </c>
       <c r="F34" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C35">
-        <v>1040012</v>
+        <v>1050120</v>
       </c>
       <c r="D35" t="s">
         <v>50</v>
       </c>
       <c r="F35" t="s">
-        <v>89</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C36">
-        <v>1040013</v>
+        <v>1050130</v>
       </c>
       <c r="D36" t="s">
         <v>51</v>
       </c>
       <c r="F36" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B37" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37">
+        <v>1050140</v>
+      </c>
+      <c r="D37" t="s">
         <v>52</v>
       </c>
-      <c r="C37">
-        <v>1040014</v>
-      </c>
-      <c r="D37" t="s">
-        <v>53</v>
-      </c>
       <c r="F37" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C38">
-        <v>1040015</v>
+        <v>9000000</v>
       </c>
       <c r="D38" t="s">
         <v>54</v>
       </c>
       <c r="F38" t="s">
-        <v>84</v>
+        <v>62</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B39" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C39">
-        <v>1040016</v>
+        <v>9000010</v>
       </c>
       <c r="D39" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F39" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B40" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C40">
-        <v>1040017</v>
+        <v>9000020</v>
       </c>
       <c r="D40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F40" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B41" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C41">
-        <v>1050000</v>
+        <v>9000030</v>
       </c>
       <c r="D41" t="s">
+        <v>57</v>
+      </c>
+      <c r="F41" t="s">
         <v>61</v>
-      </c>
-      <c r="F41" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B42" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C42">
-        <v>1050010</v>
+        <v>9000040</v>
       </c>
       <c r="D42" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F42" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B43" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C43">
-        <v>1050020</v>
+        <v>9000050</v>
       </c>
       <c r="D43" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F43" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B44" t="s">
-        <v>60</v>
-      </c>
-      <c r="C44">
-        <v>1050030</v>
-      </c>
-      <c r="D44" t="s">
-        <v>66</v>
-      </c>
-      <c r="F44" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" t="s">
-        <v>60</v>
-      </c>
-      <c r="C45">
-        <v>1050040</v>
-      </c>
-      <c r="D45" t="s">
-        <v>67</v>
-      </c>
-      <c r="F45" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B46" t="s">
-        <v>60</v>
-      </c>
-      <c r="C46">
-        <v>1050050</v>
-      </c>
-      <c r="D46" t="s">
-        <v>63</v>
-      </c>
-      <c r="F46" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B47" t="s">
-        <v>60</v>
-      </c>
-      <c r="C47">
-        <v>1050060</v>
-      </c>
-      <c r="D47" t="s">
-        <v>64</v>
-      </c>
-      <c r="F47" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B48" t="s">
-        <v>60</v>
-      </c>
-      <c r="C48">
-        <v>1050070</v>
-      </c>
-      <c r="D48" t="s">
-        <v>68</v>
-      </c>
-      <c r="F48" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B49" t="s">
-        <v>60</v>
-      </c>
-      <c r="C49">
-        <v>1050080</v>
-      </c>
-      <c r="D49" t="s">
-        <v>69</v>
-      </c>
-      <c r="F49" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B50" t="s">
-        <v>60</v>
-      </c>
-      <c r="C50">
-        <v>1050090</v>
-      </c>
-      <c r="D50" t="s">
-        <v>70</v>
-      </c>
-      <c r="F50" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" t="s">
-        <v>60</v>
-      </c>
-      <c r="C51">
-        <v>1050100</v>
-      </c>
-      <c r="D51" t="s">
-        <v>71</v>
-      </c>
-      <c r="F51" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B52" t="s">
-        <v>60</v>
-      </c>
-      <c r="C52">
-        <v>1050110</v>
-      </c>
-      <c r="D52" t="s">
-        <v>72</v>
-      </c>
-      <c r="F52" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B53" t="s">
-        <v>60</v>
-      </c>
-      <c r="C53">
-        <v>1050120</v>
-      </c>
-      <c r="D53" t="s">
-        <v>73</v>
-      </c>
-      <c r="F53" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B54" t="s">
-        <v>60</v>
-      </c>
-      <c r="C54">
-        <v>1050130</v>
-      </c>
-      <c r="D54" t="s">
-        <v>74</v>
-      </c>
-      <c r="F54" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B55" t="s">
-        <v>60</v>
-      </c>
-      <c r="C55">
-        <v>1050140</v>
-      </c>
-      <c r="D55" t="s">
-        <v>75</v>
-      </c>
-      <c r="F55" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B56" t="s">
-        <v>76</v>
-      </c>
-      <c r="C56">
-        <v>9000000</v>
-      </c>
-      <c r="D56" t="s">
-        <v>77</v>
-      </c>
-      <c r="F56" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B57" t="s">
-        <v>76</v>
-      </c>
-      <c r="C57">
-        <v>9000010</v>
-      </c>
-      <c r="D57" t="s">
-        <v>78</v>
-      </c>
-      <c r="F57" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B58" t="s">
-        <v>76</v>
-      </c>
-      <c r="C58">
-        <v>9000020</v>
-      </c>
-      <c r="D58" t="s">
-        <v>79</v>
-      </c>
-      <c r="F58" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B59" t="s">
-        <v>76</v>
-      </c>
-      <c r="C59">
-        <v>9000030</v>
-      </c>
-      <c r="D59" t="s">
-        <v>80</v>
-      </c>
-      <c r="F59" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B60" t="s">
-        <v>76</v>
-      </c>
-      <c r="C60">
-        <v>9000040</v>
-      </c>
-      <c r="D60" t="s">
-        <v>81</v>
-      </c>
-      <c r="F60" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B61" t="s">
-        <v>76</v>
-      </c>
-      <c r="C61">
-        <v>9000050</v>
-      </c>
-      <c r="D61" t="s">
-        <v>82</v>
-      </c>
-      <c r="F61" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>